--- a/artfynd/A 39776-2026 artfynd.xlsx
+++ b/artfynd/A 39776-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137417719</v>
       </c>
       <c r="B2" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137407783</v>
       </c>
       <c r="B3" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137407939</v>
       </c>
       <c r="B4" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39776-2026 artfynd.xlsx
+++ b/artfynd/A 39776-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137417719</v>
       </c>
       <c r="B2" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137407783</v>
       </c>
       <c r="B3" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137407939</v>
       </c>
       <c r="B4" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39776-2026 artfynd.xlsx
+++ b/artfynd/A 39776-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137417719</v>
       </c>
       <c r="B2" t="n">
-        <v>92396</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137407783</v>
       </c>
       <c r="B3" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137407939</v>
       </c>
       <c r="B4" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39776-2026 artfynd.xlsx
+++ b/artfynd/A 39776-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137417719</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137407783</v>
       </c>
       <c r="B3" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137407939</v>
       </c>
       <c r="B4" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>137407812</v>
       </c>
       <c r="B5" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137408058</v>
       </c>
       <c r="B6" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>137410810</v>
       </c>
       <c r="B7" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
